--- a/Stock_OneClick/history/scan_result_20260526_074532.xlsx
+++ b/Stock_OneClick/history/scan_result_20260526_074532.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="RawSignals" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="买入观察列表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="买入历史记录" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="卖出观察列表" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="卖出历史记录" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="2026-05-22" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="2026-05-25" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="2026-05-26" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RawSignals" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="买入观察列表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="买入历史记录" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="卖出观察列表" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="卖出历史记录" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-05-22" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-05-25" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-05-26" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q61"/>
+  <dimension ref="A1:Q59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -634,24 +634,12 @@
       <c r="J3" s="4" t="n">
         <v>205.76</v>
       </c>
-      <c r="K3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P3" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K3" s="4" t="n"/>
+      <c r="L3" s="4" t="n"/>
+      <c r="M3" s="4" t="n"/>
+      <c r="N3" s="4" t="n"/>
+      <c r="O3" s="4" t="n"/>
+      <c r="P3" s="4" t="n"/>
       <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>D0=202.91; 最新=2026-05-26; 相对D0=1.40%; 本次触发=2026-05-26(正式买入 | 预警买入); 历史重复1次; 重复日期=2026-05-26</t>
@@ -703,24 +691,12 @@
       <c r="J4" s="4" t="n">
         <v>173.03</v>
       </c>
-      <c r="K4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P4" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K4" s="4" t="n"/>
+      <c r="L4" s="4" t="n"/>
+      <c r="M4" s="4" t="n"/>
+      <c r="N4" s="4" t="n"/>
+      <c r="O4" s="4" t="n"/>
+      <c r="P4" s="4" t="n"/>
       <c r="Q4" s="4" t="inlineStr">
         <is>
           <t>D0=167.37; 最新=2026-05-26; 相对D0=3.38%; 本次触发=2026-05-26(正式买入); 历史重复1次; 重复日期=2026-05-26</t>
@@ -772,24 +748,12 @@
       <c r="J5" s="4" t="n">
         <v>50.34</v>
       </c>
-      <c r="K5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P5" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K5" s="4" t="n"/>
+      <c r="L5" s="4" t="n"/>
+      <c r="M5" s="4" t="n"/>
+      <c r="N5" s="4" t="n"/>
+      <c r="O5" s="4" t="n"/>
+      <c r="P5" s="4" t="n"/>
       <c r="Q5" s="4" t="inlineStr">
         <is>
           <t>D0=48.12; 最新=2026-05-26; 相对D0=4.61%; 本次触发=2026-05-26(正式买入); 历史重复1次; 重复日期=2026-05-26</t>
@@ -841,24 +805,12 @@
       <c r="J6" s="4" t="n">
         <v>408.715</v>
       </c>
-      <c r="K6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P6" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K6" s="4" t="n"/>
+      <c r="L6" s="4" t="n"/>
+      <c r="M6" s="4" t="n"/>
+      <c r="N6" s="4" t="n"/>
+      <c r="O6" s="4" t="n"/>
+      <c r="P6" s="4" t="n"/>
       <c r="Q6" s="4" t="inlineStr">
         <is>
           <t>D0=391.35; 最新=2026-05-26; 相对D0=4.44%; 本次触发=2026-05-26(正式买入); 历史重复1次; 重复日期=2026-05-26</t>
@@ -910,24 +862,12 @@
       <c r="J7" s="4" t="n">
         <v>1091</v>
       </c>
-      <c r="K7" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L7" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M7" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N7" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O7" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P7" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K7" s="4" t="n"/>
+      <c r="L7" s="4" t="n"/>
+      <c r="M7" s="4" t="n"/>
+      <c r="N7" s="4" t="n"/>
+      <c r="O7" s="4" t="n"/>
+      <c r="P7" s="4" t="n"/>
       <c r="Q7" s="4" t="inlineStr">
         <is>
           <t>D0=1038.74; 最新=2026-05-26; 相对D0=5.03%; 本次触发=2026-05-26(正式买入 | 预警买入); 历史重复1次; 重复日期=2026-05-26</t>
@@ -979,24 +919,12 @@
       <c r="J8" s="4" t="n">
         <v>187.29</v>
       </c>
-      <c r="K8" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L8" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M8" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N8" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O8" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P8" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K8" s="4" t="n"/>
+      <c r="L8" s="4" t="n"/>
+      <c r="M8" s="4" t="n"/>
+      <c r="N8" s="4" t="n"/>
+      <c r="O8" s="4" t="n"/>
+      <c r="P8" s="4" t="n"/>
       <c r="Q8" s="4" t="inlineStr">
         <is>
           <t>D0=179.36; 最新=2026-05-26; 相对D0=4.42%; 本次触发=2026-05-26(正式买入); 历史重复1次; 重复日期=2026-05-26</t>
@@ -1048,27 +976,9 @@
       <c r="J9" t="n">
         <v>22.955</v>
       </c>
-      <c r="K9" t="n">
-        <v/>
-      </c>
-      <c r="L9" t="n">
-        <v/>
-      </c>
-      <c r="M9" t="n">
-        <v/>
-      </c>
-      <c r="N9" t="n">
-        <v/>
-      </c>
-      <c r="O9" t="n">
-        <v/>
-      </c>
-      <c r="P9" t="n">
-        <v/>
-      </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>D0=22.51; 最新=2026-05-26; 相对D0=1.98%; 本次触发=2026-05-26(第一买入点); 历史重复1次; 重复日期=2026-05-26</t>
+          <t>D0=22.51; 最新=2026-05-26; 相对D0=1.98%; 本次触发=2026-05-26(第一观察点); 历史重复1次; 重复日期=2026-05-26</t>
         </is>
       </c>
     </row>
@@ -1117,24 +1027,12 @@
       <c r="J10" s="4" t="n">
         <v>276.195</v>
       </c>
-      <c r="K10" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L10" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M10" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N10" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O10" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P10" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K10" s="4" t="n"/>
+      <c r="L10" s="4" t="n"/>
+      <c r="M10" s="4" t="n"/>
+      <c r="N10" s="4" t="n"/>
+      <c r="O10" s="4" t="n"/>
+      <c r="P10" s="4" t="n"/>
       <c r="Q10" s="4" t="inlineStr">
         <is>
           <t>D0=262.25; 最新=2026-05-26; 相对D0=5.32%; 本次触发=2026-05-26(正式买入 | 预警买入); 历史重复1次; 重复日期=2026-05-26</t>
@@ -1186,24 +1084,12 @@
       <c r="J11" s="4" t="n">
         <v>13.62</v>
       </c>
-      <c r="K11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P11" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K11" s="4" t="n"/>
+      <c r="L11" s="4" t="n"/>
+      <c r="M11" s="4" t="n"/>
+      <c r="N11" s="4" t="n"/>
+      <c r="O11" s="4" t="n"/>
+      <c r="P11" s="4" t="n"/>
       <c r="Q11" s="4" t="inlineStr">
         <is>
           <t>D0=13.02; 最新=2026-05-26; 相对D0=4.61%; 本次触发=2026-05-26(正式买入 | 预警买入); 历史重复1次; 重复日期=2026-05-26</t>
@@ -1255,24 +1141,12 @@
       <c r="J12" s="4" t="n">
         <v>75.83</v>
       </c>
-      <c r="K12" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L12" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M12" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N12" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O12" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P12" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K12" s="4" t="n"/>
+      <c r="L12" s="4" t="n"/>
+      <c r="M12" s="4" t="n"/>
+      <c r="N12" s="4" t="n"/>
+      <c r="O12" s="4" t="n"/>
+      <c r="P12" s="4" t="n"/>
       <c r="Q12" s="4" t="inlineStr">
         <is>
           <t>D0=75.83; 最新=2026-05-26; 相对D0=0.00%; 本次触发=2026-05-26(正式买入 | 预警买入)</t>
@@ -1324,24 +1198,6 @@
       <c r="J13" t="n">
         <v>432.46</v>
       </c>
-      <c r="K13" t="n">
-        <v/>
-      </c>
-      <c r="L13" t="n">
-        <v/>
-      </c>
-      <c r="M13" t="n">
-        <v/>
-      </c>
-      <c r="N13" t="n">
-        <v/>
-      </c>
-      <c r="O13" t="n">
-        <v/>
-      </c>
-      <c r="P13" t="n">
-        <v/>
-      </c>
       <c r="Q13" t="inlineStr">
         <is>
           <t>D0=432.46; 最新=2026-05-26; 相对D0=0.00%; 本次触发=2026-05-26(正式买入 | 预警买入)</t>
@@ -1393,24 +1249,12 @@
       <c r="J14" s="4" t="n">
         <v>86.25</v>
       </c>
-      <c r="K14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P14" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K14" s="4" t="n"/>
+      <c r="L14" s="4" t="n"/>
+      <c r="M14" s="4" t="n"/>
+      <c r="N14" s="4" t="n"/>
+      <c r="O14" s="4" t="n"/>
+      <c r="P14" s="4" t="n"/>
       <c r="Q14" s="4" t="inlineStr">
         <is>
           <t>D0=86.25; 最新=2026-05-26; 相对D0=0.00%; 本次触发=2026-05-26(预警买入)</t>
@@ -1462,24 +1306,12 @@
       <c r="J15" s="4" t="n">
         <v>108.24</v>
       </c>
-      <c r="K15" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L15" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M15" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N15" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O15" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P15" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K15" s="4" t="n"/>
+      <c r="L15" s="4" t="n"/>
+      <c r="M15" s="4" t="n"/>
+      <c r="N15" s="4" t="n"/>
+      <c r="O15" s="4" t="n"/>
+      <c r="P15" s="4" t="n"/>
       <c r="Q15" s="4" t="inlineStr">
         <is>
           <t>D0=108.24; 最新=2026-05-26; 相对D0=0.00%; 本次触发=2026-05-26(预警买入)</t>
@@ -1531,24 +1363,6 @@
       <c r="J16" t="n">
         <v>107.23</v>
       </c>
-      <c r="K16" t="n">
-        <v/>
-      </c>
-      <c r="L16" t="n">
-        <v/>
-      </c>
-      <c r="M16" t="n">
-        <v/>
-      </c>
-      <c r="N16" t="n">
-        <v/>
-      </c>
-      <c r="O16" t="n">
-        <v/>
-      </c>
-      <c r="P16" t="n">
-        <v/>
-      </c>
       <c r="Q16" t="inlineStr">
         <is>
           <t>D0=107.23; 最新=2026-05-26; 相对D0=0.00%; 本次触发=2026-05-26(预警买入)</t>
@@ -1600,24 +1414,6 @@
       <c r="J17" t="n">
         <v>87.7</v>
       </c>
-      <c r="K17" t="n">
-        <v/>
-      </c>
-      <c r="L17" t="n">
-        <v/>
-      </c>
-      <c r="M17" t="n">
-        <v/>
-      </c>
-      <c r="N17" t="n">
-        <v/>
-      </c>
-      <c r="O17" t="n">
-        <v/>
-      </c>
-      <c r="P17" t="n">
-        <v/>
-      </c>
       <c r="Q17" t="inlineStr">
         <is>
           <t>D0=87.70; 最新=2026-05-26; 相对D0=0.00%; 本次触发=2026-05-26(预警买入)</t>
@@ -1669,24 +1465,6 @@
       <c r="J18" t="n">
         <v>154.68</v>
       </c>
-      <c r="K18" t="n">
-        <v/>
-      </c>
-      <c r="L18" t="n">
-        <v/>
-      </c>
-      <c r="M18" t="n">
-        <v/>
-      </c>
-      <c r="N18" t="n">
-        <v/>
-      </c>
-      <c r="O18" t="n">
-        <v/>
-      </c>
-      <c r="P18" t="n">
-        <v/>
-      </c>
       <c r="Q18" t="inlineStr">
         <is>
           <t>D0=154.68; 最新=2026-05-26; 相对D0=0.00%; 本次触发=2026-05-26(预警买入)</t>
@@ -1738,27 +1516,15 @@
       <c r="J19" s="4" t="n">
         <v>70.68000000000001</v>
       </c>
-      <c r="K19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P19" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K19" s="4" t="n"/>
+      <c r="L19" s="4" t="n"/>
+      <c r="M19" s="4" t="n"/>
+      <c r="N19" s="4" t="n"/>
+      <c r="O19" s="4" t="n"/>
+      <c r="P19" s="4" t="n"/>
       <c r="Q19" s="4" t="inlineStr">
         <is>
-          <t>D0=70.68; 最新=2026-05-26; 相对D0=0.00%; 本次触发=2026-05-26(第一买入点)</t>
+          <t>D0=70.68; 最新=2026-05-26; 相对D0=0.00%; 本次触发=2026-05-26(第一观察点)</t>
         </is>
       </c>
     </row>
@@ -1807,24 +1573,12 @@
       <c r="J20" s="4" t="n">
         <v>106.725</v>
       </c>
-      <c r="K20" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L20" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M20" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N20" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O20" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P20" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K20" s="4" t="n"/>
+      <c r="L20" s="4" t="n"/>
+      <c r="M20" s="4" t="n"/>
+      <c r="N20" s="4" t="n"/>
+      <c r="O20" s="4" t="n"/>
+      <c r="P20" s="4" t="n"/>
       <c r="Q20" s="4" t="inlineStr">
         <is>
           <t>D0=106.72; 最新=2026-05-26; 相对D0=0.00%; 本次触发=2026-05-26(正式买入 | 预警买入)</t>
@@ -1876,27 +1630,15 @@
       <c r="J21" s="4" t="n">
         <v>12.52</v>
       </c>
-      <c r="K21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P21" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K21" s="4" t="n"/>
+      <c r="L21" s="4" t="n"/>
+      <c r="M21" s="4" t="n"/>
+      <c r="N21" s="4" t="n"/>
+      <c r="O21" s="4" t="n"/>
+      <c r="P21" s="4" t="n"/>
       <c r="Q21" s="4" t="inlineStr">
         <is>
-          <t>D0=12.52; 最新=2026-05-26; 相对D0=0.00%; 本次触发=2026-05-26(第一买入点)</t>
+          <t>D0=12.52; 最新=2026-05-26; 相对D0=0.00%; 本次触发=2026-05-26(第一观察点)</t>
         </is>
       </c>
     </row>
@@ -1945,24 +1687,6 @@
       <c r="J22" t="n">
         <v>82.545</v>
       </c>
-      <c r="K22" t="n">
-        <v/>
-      </c>
-      <c r="L22" t="n">
-        <v/>
-      </c>
-      <c r="M22" t="n">
-        <v/>
-      </c>
-      <c r="N22" t="n">
-        <v/>
-      </c>
-      <c r="O22" t="n">
-        <v/>
-      </c>
-      <c r="P22" t="n">
-        <v/>
-      </c>
       <c r="Q22" t="inlineStr">
         <is>
           <t>D0=82.55; 最新=2026-05-26; 相对D0=0.00%; 本次触发=2026-05-26(正式买入 | 预警买入)</t>
@@ -2014,24 +1738,12 @@
       <c r="J23" s="4" t="n">
         <v>18.885</v>
       </c>
-      <c r="K23" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L23" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M23" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N23" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O23" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P23" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K23" s="4" t="n"/>
+      <c r="L23" s="4" t="n"/>
+      <c r="M23" s="4" t="n"/>
+      <c r="N23" s="4" t="n"/>
+      <c r="O23" s="4" t="n"/>
+      <c r="P23" s="4" t="n"/>
       <c r="Q23" s="4" t="inlineStr">
         <is>
           <t>D0=18.89; 最新=2026-05-26; 相对D0=0.00%; 本次触发=2026-05-26(正式买入)</t>
@@ -2083,24 +1795,6 @@
       <c r="J24" t="n">
         <v>338.585</v>
       </c>
-      <c r="K24" t="n">
-        <v/>
-      </c>
-      <c r="L24" t="n">
-        <v/>
-      </c>
-      <c r="M24" t="n">
-        <v/>
-      </c>
-      <c r="N24" t="n">
-        <v/>
-      </c>
-      <c r="O24" t="n">
-        <v/>
-      </c>
-      <c r="P24" t="n">
-        <v/>
-      </c>
       <c r="Q24" t="inlineStr">
         <is>
           <t>D0=338.58; 最新=2026-05-26; 相对D0=0.00%; 本次触发=2026-05-26(正式买入 | 预警买入)</t>
@@ -2152,24 +1846,6 @@
       <c r="J25" t="n">
         <v>181.9</v>
       </c>
-      <c r="K25" t="n">
-        <v/>
-      </c>
-      <c r="L25" t="n">
-        <v/>
-      </c>
-      <c r="M25" t="n">
-        <v/>
-      </c>
-      <c r="N25" t="n">
-        <v/>
-      </c>
-      <c r="O25" t="n">
-        <v/>
-      </c>
-      <c r="P25" t="n">
-        <v/>
-      </c>
       <c r="Q25" t="inlineStr">
         <is>
           <t>D0=181.49; 最新=2026-05-26; 相对D0=0.23%</t>
@@ -2221,24 +1897,12 @@
       <c r="J26" s="4" t="n">
         <v>47.97</v>
       </c>
-      <c r="K26" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L26" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M26" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N26" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O26" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P26" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K26" s="4" t="n"/>
+      <c r="L26" s="4" t="n"/>
+      <c r="M26" s="4" t="n"/>
+      <c r="N26" s="4" t="n"/>
+      <c r="O26" s="4" t="n"/>
+      <c r="P26" s="4" t="n"/>
       <c r="Q26" s="4" t="inlineStr">
         <is>
           <t>D0=46.53; 最新=2026-05-26; 相对D0=3.09%</t>
@@ -2290,24 +1954,6 @@
       <c r="J27" t="n">
         <v>15.845</v>
       </c>
-      <c r="K27" t="n">
-        <v/>
-      </c>
-      <c r="L27" t="n">
-        <v/>
-      </c>
-      <c r="M27" t="n">
-        <v/>
-      </c>
-      <c r="N27" t="n">
-        <v/>
-      </c>
-      <c r="O27" t="n">
-        <v/>
-      </c>
-      <c r="P27" t="n">
-        <v/>
-      </c>
       <c r="Q27" t="inlineStr">
         <is>
           <t>D0=16.12; 最新=2026-05-26; 相对D0=-1.71%</t>
@@ -2359,24 +2005,12 @@
       <c r="J28" s="4" t="n">
         <v>181.335</v>
       </c>
-      <c r="K28" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L28" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M28" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N28" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O28" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P28" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K28" s="4" t="n"/>
+      <c r="L28" s="4" t="n"/>
+      <c r="M28" s="4" t="n"/>
+      <c r="N28" s="4" t="n"/>
+      <c r="O28" s="4" t="n"/>
+      <c r="P28" s="4" t="n"/>
       <c r="Q28" s="4" t="inlineStr">
         <is>
           <t>D0=180.07; 最新=2026-05-26; 相对D0=0.70%</t>
@@ -2428,24 +2062,6 @@
       <c r="J29" t="n">
         <v>138.87</v>
       </c>
-      <c r="K29" t="n">
-        <v/>
-      </c>
-      <c r="L29" t="n">
-        <v/>
-      </c>
-      <c r="M29" t="n">
-        <v/>
-      </c>
-      <c r="N29" t="n">
-        <v/>
-      </c>
-      <c r="O29" t="n">
-        <v/>
-      </c>
-      <c r="P29" t="n">
-        <v/>
-      </c>
       <c r="Q29" t="inlineStr">
         <is>
           <t>D0=141.22; 最新=2026-05-26; 相对D0=-1.66%</t>
@@ -2497,24 +2113,12 @@
       <c r="J30" s="4" t="n">
         <v>309.64</v>
       </c>
-      <c r="K30" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L30" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M30" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N30" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O30" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P30" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K30" s="4" t="n"/>
+      <c r="L30" s="4" t="n"/>
+      <c r="M30" s="4" t="n"/>
+      <c r="N30" s="4" t="n"/>
+      <c r="O30" s="4" t="n"/>
+      <c r="P30" s="4" t="n"/>
       <c r="Q30" s="4" t="inlineStr">
         <is>
           <t>D0=326.13; 最新=2026-05-26; 相对D0=-5.06%</t>
@@ -2566,24 +2170,12 @@
       <c r="J31" s="4" t="n">
         <v>239.61</v>
       </c>
-      <c r="K31" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L31" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M31" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N31" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O31" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P31" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K31" s="4" t="n"/>
+      <c r="L31" s="4" t="n"/>
+      <c r="M31" s="4" t="n"/>
+      <c r="N31" s="4" t="n"/>
+      <c r="O31" s="4" t="n"/>
+      <c r="P31" s="4" t="n"/>
       <c r="Q31" s="4" t="inlineStr">
         <is>
           <t>D0=232.00; 最新=2026-05-26; 相对D0=3.28%</t>
@@ -2635,24 +2227,6 @@
       <c r="J32" t="n">
         <v>129.01</v>
       </c>
-      <c r="K32" t="n">
-        <v/>
-      </c>
-      <c r="L32" t="n">
-        <v/>
-      </c>
-      <c r="M32" t="n">
-        <v/>
-      </c>
-      <c r="N32" t="n">
-        <v/>
-      </c>
-      <c r="O32" t="n">
-        <v/>
-      </c>
-      <c r="P32" t="n">
-        <v/>
-      </c>
       <c r="Q32" t="inlineStr">
         <is>
           <t>D0=130.50; 最新=2026-05-26; 相对D0=-1.14%</t>
@@ -2704,24 +2278,12 @@
       <c r="J33" s="4" t="n">
         <v>84.8331</v>
       </c>
-      <c r="K33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P33" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K33" s="4" t="n"/>
+      <c r="L33" s="4" t="n"/>
+      <c r="M33" s="4" t="n"/>
+      <c r="N33" s="4" t="n"/>
+      <c r="O33" s="4" t="n"/>
+      <c r="P33" s="4" t="n"/>
       <c r="Q33" s="4" t="inlineStr">
         <is>
           <t>D0=85.42; 最新=2026-05-26; 相对D0=-0.69%</t>
@@ -2772,24 +2334,6 @@
       </c>
       <c r="J34" t="n">
         <v>431.81</v>
-      </c>
-      <c r="K34" t="n">
-        <v/>
-      </c>
-      <c r="L34" t="n">
-        <v/>
-      </c>
-      <c r="M34" t="n">
-        <v/>
-      </c>
-      <c r="N34" t="n">
-        <v/>
-      </c>
-      <c r="O34" t="n">
-        <v/>
-      </c>
-      <c r="P34" t="n">
-        <v/>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -3027,24 +2571,12 @@
       <c r="J46" s="4" t="n">
         <v>186.54</v>
       </c>
-      <c r="K46" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L46" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M46" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N46" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O46" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P46" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K46" s="4" t="n"/>
+      <c r="L46" s="4" t="n"/>
+      <c r="M46" s="4" t="n"/>
+      <c r="N46" s="4" t="n"/>
+      <c r="O46" s="4" t="n"/>
+      <c r="P46" s="4" t="n"/>
       <c r="Q46" s="4" t="inlineStr">
         <is>
           <t>D0=186.54; 最新=2026-05-26; 相对D0=0.00%; 本次触发=2026-05-26(正式卖出)</t>
@@ -3096,24 +2628,12 @@
       <c r="J47" s="4" t="n">
         <v>138.87</v>
       </c>
-      <c r="K47" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L47" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M47" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N47" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O47" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P47" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K47" s="4" t="n"/>
+      <c r="L47" s="4" t="n"/>
+      <c r="M47" s="4" t="n"/>
+      <c r="N47" s="4" t="n"/>
+      <c r="O47" s="4" t="n"/>
+      <c r="P47" s="4" t="n"/>
       <c r="Q47" s="4" t="inlineStr">
         <is>
           <t>D0=138.87; 最新=2026-05-26; 相对D0=0.00%; 本次触发=2026-05-26(正式卖出)</t>
@@ -3165,24 +2685,12 @@
       <c r="J48" s="4" t="n">
         <v>38.71</v>
       </c>
-      <c r="K48" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L48" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M48" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N48" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O48" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P48" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K48" s="4" t="n"/>
+      <c r="L48" s="4" t="n"/>
+      <c r="M48" s="4" t="n"/>
+      <c r="N48" s="4" t="n"/>
+      <c r="O48" s="4" t="n"/>
+      <c r="P48" s="4" t="n"/>
       <c r="Q48" s="4" t="inlineStr">
         <is>
           <t>D0=38.71; 最新=2026-05-26; 相对D0=0.00%; 本次触发=2026-05-26(正式卖出 | 预警卖出)</t>
@@ -3234,24 +2742,12 @@
       <c r="J49" s="4" t="n">
         <v>309.64</v>
       </c>
-      <c r="K49" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L49" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M49" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N49" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O49" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P49" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K49" s="4" t="n"/>
+      <c r="L49" s="4" t="n"/>
+      <c r="M49" s="4" t="n"/>
+      <c r="N49" s="4" t="n"/>
+      <c r="O49" s="4" t="n"/>
+      <c r="P49" s="4" t="n"/>
       <c r="Q49" s="4" t="inlineStr">
         <is>
           <t>D0=309.64; 最新=2026-05-26; 相对D0=0.00%; 本次触发=2026-05-26(正式卖出)</t>
@@ -3303,24 +2799,12 @@
       <c r="J50" s="4" t="n">
         <v>58.315</v>
       </c>
-      <c r="K50" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L50" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M50" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N50" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O50" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P50" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K50" s="4" t="n"/>
+      <c r="L50" s="4" t="n"/>
+      <c r="M50" s="4" t="n"/>
+      <c r="N50" s="4" t="n"/>
+      <c r="O50" s="4" t="n"/>
+      <c r="P50" s="4" t="n"/>
       <c r="Q50" s="4" t="inlineStr">
         <is>
           <t>D0=58.31; 最新=2026-05-26; 相对D0=0.00%; 本次触发=2026-05-26(正式卖出)</t>
@@ -3372,24 +2856,12 @@
       <c r="J51" s="4" t="n">
         <v>13.5301</v>
       </c>
-      <c r="K51" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L51" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M51" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N51" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O51" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P51" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K51" s="4" t="n"/>
+      <c r="L51" s="4" t="n"/>
+      <c r="M51" s="4" t="n"/>
+      <c r="N51" s="4" t="n"/>
+      <c r="O51" s="4" t="n"/>
+      <c r="P51" s="4" t="n"/>
       <c r="Q51" s="4" t="inlineStr">
         <is>
           <t>D0=13.53; 最新=2026-05-26; 相对D0=0.00%; 本次触发=2026-05-26(正式卖出)</t>
@@ -3441,24 +2913,12 @@
       <c r="J52" s="4" t="n">
         <v>41.08</v>
       </c>
-      <c r="K52" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L52" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M52" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N52" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O52" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P52" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K52" s="4" t="n"/>
+      <c r="L52" s="4" t="n"/>
+      <c r="M52" s="4" t="n"/>
+      <c r="N52" s="4" t="n"/>
+      <c r="O52" s="4" t="n"/>
+      <c r="P52" s="4" t="n"/>
       <c r="Q52" s="4" t="inlineStr">
         <is>
           <t>D0=41.47; 最新=2026-05-26; 相对D0=-0.94%</t>
@@ -3542,8 +3002,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60"/>
-    <row r="61"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4620,8 +4078,6 @@
       <c r="T12" t="b">
         <v>0</v>
       </c>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
           <t>4H 0出; 4H_RSI=46.20; 4H分金=60.51</t>
@@ -4703,8 +4159,6 @@
       <c r="T13" t="b">
         <v>0</v>
       </c>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
         <is>
           <t>4H 0出; 4H_RSI=47.47; 4H分金=55.06</t>
@@ -5134,8 +4588,6 @@
       <c r="T18" t="b">
         <v>0</v>
       </c>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr">
         <is>
           <t>4H 0出; 4H_RSI=46.28; 4H分金=56.07</t>
@@ -5391,8 +4843,6 @@
       <c r="T21" t="b">
         <v>0</v>
       </c>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr">
         <is>
           <t>4H 0出; 4H_RSI=43.14; 4H分金=52.61</t>
@@ -5822,8 +5272,6 @@
       <c r="T26" t="b">
         <v>1</v>
       </c>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=41.19; 4H分金=35.40</t>
@@ -5946,7 +5394,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -6033,7 +5481,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -6729,7 +6177,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -7548,7 +6996,6 @@
       <c r="D2" s="8" t="n">
         <v>46164</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" s="8" t="n">
         <v>46164</v>
       </c>
@@ -7600,7 +7047,6 @@
       <c r="D3" s="8" t="n">
         <v>46164</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" s="8" t="n">
         <v>46164</v>
       </c>
@@ -7706,7 +7152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -7934,7 +7380,6 @@
       <c r="G7" s="11" t="n">
         <v>-0.01706</v>
       </c>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -8034,7 +7479,6 @@
       <c r="G10" s="11" t="n">
         <v>-0.016641</v>
       </c>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -8242,7 +7686,6 @@
       <c r="G16" s="13" t="n">
         <v>0.032802</v>
       </c>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8274,7 +7717,6 @@
       <c r="G17" s="11" t="n">
         <v>-0.011418</v>
       </c>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -8374,7 +7816,6 @@
       <c r="G20" s="13" t="n">
         <v>0.013615</v>
       </c>
-      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -8622,11 +8063,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8638,7 +8074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q42"/>
+  <dimension ref="A1:Q37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -8799,24 +8235,12 @@
       <c r="J3" s="4" t="n">
         <v>181.49</v>
       </c>
-      <c r="K3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P3" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K3" s="4" t="n"/>
+      <c r="L3" s="4" t="n"/>
+      <c r="M3" s="4" t="n"/>
+      <c r="N3" s="4" t="n"/>
+      <c r="O3" s="4" t="n"/>
+      <c r="P3" s="4" t="n"/>
       <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>D0=181.49; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -8868,24 +8292,12 @@
       <c r="J4" s="4" t="n">
         <v>202.91</v>
       </c>
-      <c r="K4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P4" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K4" s="4" t="n"/>
+      <c r="L4" s="4" t="n"/>
+      <c r="M4" s="4" t="n"/>
+      <c r="N4" s="4" t="n"/>
+      <c r="O4" s="4" t="n"/>
+      <c r="P4" s="4" t="n"/>
       <c r="Q4" s="4" t="inlineStr">
         <is>
           <t>D0=202.91; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -8937,24 +8349,12 @@
       <c r="J5" s="4" t="n">
         <v>167.37</v>
       </c>
-      <c r="K5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P5" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K5" s="4" t="n"/>
+      <c r="L5" s="4" t="n"/>
+      <c r="M5" s="4" t="n"/>
+      <c r="N5" s="4" t="n"/>
+      <c r="O5" s="4" t="n"/>
+      <c r="P5" s="4" t="n"/>
       <c r="Q5" s="4" t="inlineStr">
         <is>
           <t>D0=167.37; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -9006,24 +8406,12 @@
       <c r="J6" s="4" t="n">
         <v>46.53</v>
       </c>
-      <c r="K6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P6" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K6" s="4" t="n"/>
+      <c r="L6" s="4" t="n"/>
+      <c r="M6" s="4" t="n"/>
+      <c r="N6" s="4" t="n"/>
+      <c r="O6" s="4" t="n"/>
+      <c r="P6" s="4" t="n"/>
       <c r="Q6" s="4" t="inlineStr">
         <is>
           <t>D0=46.53; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -9075,24 +8463,6 @@
       <c r="J7" t="n">
         <v>16.12</v>
       </c>
-      <c r="K7" t="n">
-        <v/>
-      </c>
-      <c r="L7" t="n">
-        <v/>
-      </c>
-      <c r="M7" t="n">
-        <v/>
-      </c>
-      <c r="N7" t="n">
-        <v/>
-      </c>
-      <c r="O7" t="n">
-        <v/>
-      </c>
-      <c r="P7" t="n">
-        <v/>
-      </c>
       <c r="Q7" t="inlineStr">
         <is>
           <t>D0=16.12; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -9144,24 +8514,12 @@
       <c r="J8" s="4" t="n">
         <v>180.07</v>
       </c>
-      <c r="K8" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L8" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M8" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N8" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O8" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P8" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K8" s="4" t="n"/>
+      <c r="L8" s="4" t="n"/>
+      <c r="M8" s="4" t="n"/>
+      <c r="N8" s="4" t="n"/>
+      <c r="O8" s="4" t="n"/>
+      <c r="P8" s="4" t="n"/>
       <c r="Q8" s="4" t="inlineStr">
         <is>
           <t>D0=180.07; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -9213,24 +8571,12 @@
       <c r="J9" s="4" t="n">
         <v>48.12</v>
       </c>
-      <c r="K9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P9" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K9" s="4" t="n"/>
+      <c r="L9" s="4" t="n"/>
+      <c r="M9" s="4" t="n"/>
+      <c r="N9" s="4" t="n"/>
+      <c r="O9" s="4" t="n"/>
+      <c r="P9" s="4" t="n"/>
       <c r="Q9" s="4" t="inlineStr">
         <is>
           <t>D0=48.12; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -9282,24 +8628,6 @@
       <c r="J10" t="n">
         <v>141.22</v>
       </c>
-      <c r="K10" t="n">
-        <v/>
-      </c>
-      <c r="L10" t="n">
-        <v/>
-      </c>
-      <c r="M10" t="n">
-        <v/>
-      </c>
-      <c r="N10" t="n">
-        <v/>
-      </c>
-      <c r="O10" t="n">
-        <v/>
-      </c>
-      <c r="P10" t="n">
-        <v/>
-      </c>
       <c r="Q10" t="inlineStr">
         <is>
           <t>D0=141.22; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -9351,24 +8679,12 @@
       <c r="J11" s="4" t="n">
         <v>391.35</v>
       </c>
-      <c r="K11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P11" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K11" s="4" t="n"/>
+      <c r="L11" s="4" t="n"/>
+      <c r="M11" s="4" t="n"/>
+      <c r="N11" s="4" t="n"/>
+      <c r="O11" s="4" t="n"/>
+      <c r="P11" s="4" t="n"/>
       <c r="Q11" s="4" t="inlineStr">
         <is>
           <t>D0=391.35; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -9420,24 +8736,12 @@
       <c r="J12" s="4" t="n">
         <v>1038.74</v>
       </c>
-      <c r="K12" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L12" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M12" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N12" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O12" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P12" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K12" s="4" t="n"/>
+      <c r="L12" s="4" t="n"/>
+      <c r="M12" s="4" t="n"/>
+      <c r="N12" s="4" t="n"/>
+      <c r="O12" s="4" t="n"/>
+      <c r="P12" s="4" t="n"/>
       <c r="Q12" s="4" t="inlineStr">
         <is>
           <t>D0=1038.74; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -9489,24 +8793,12 @@
       <c r="J13" s="4" t="n">
         <v>179.36</v>
       </c>
-      <c r="K13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P13" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K13" s="4" t="n"/>
+      <c r="L13" s="4" t="n"/>
+      <c r="M13" s="4" t="n"/>
+      <c r="N13" s="4" t="n"/>
+      <c r="O13" s="4" t="n"/>
+      <c r="P13" s="4" t="n"/>
       <c r="Q13" s="4" t="inlineStr">
         <is>
           <t>D0=179.36; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -9558,24 +8850,12 @@
       <c r="J14" s="4" t="n">
         <v>326.13</v>
       </c>
-      <c r="K14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P14" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K14" s="4" t="n"/>
+      <c r="L14" s="4" t="n"/>
+      <c r="M14" s="4" t="n"/>
+      <c r="N14" s="4" t="n"/>
+      <c r="O14" s="4" t="n"/>
+      <c r="P14" s="4" t="n"/>
       <c r="Q14" s="4" t="inlineStr">
         <is>
           <t>D0=326.13; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -9627,24 +8907,6 @@
       <c r="J15" t="n">
         <v>22.51</v>
       </c>
-      <c r="K15" t="n">
-        <v/>
-      </c>
-      <c r="L15" t="n">
-        <v/>
-      </c>
-      <c r="M15" t="n">
-        <v/>
-      </c>
-      <c r="N15" t="n">
-        <v/>
-      </c>
-      <c r="O15" t="n">
-        <v/>
-      </c>
-      <c r="P15" t="n">
-        <v/>
-      </c>
       <c r="Q15" t="inlineStr">
         <is>
           <t>D0=22.51; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -9696,24 +8958,6 @@
       <c r="J16" t="n">
         <v>232</v>
       </c>
-      <c r="K16" t="n">
-        <v/>
-      </c>
-      <c r="L16" t="n">
-        <v/>
-      </c>
-      <c r="M16" t="n">
-        <v/>
-      </c>
-      <c r="N16" t="n">
-        <v/>
-      </c>
-      <c r="O16" t="n">
-        <v/>
-      </c>
-      <c r="P16" t="n">
-        <v/>
-      </c>
       <c r="Q16" t="inlineStr">
         <is>
           <t>D0=232.00; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -9765,24 +9009,6 @@
       <c r="J17" t="n">
         <v>130.5</v>
       </c>
-      <c r="K17" t="n">
-        <v/>
-      </c>
-      <c r="L17" t="n">
-        <v/>
-      </c>
-      <c r="M17" t="n">
-        <v/>
-      </c>
-      <c r="N17" t="n">
-        <v/>
-      </c>
-      <c r="O17" t="n">
-        <v/>
-      </c>
-      <c r="P17" t="n">
-        <v/>
-      </c>
       <c r="Q17" t="inlineStr">
         <is>
           <t>D0=130.50; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -9834,24 +9060,12 @@
       <c r="J18" s="4" t="n">
         <v>262.25</v>
       </c>
-      <c r="K18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P18" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K18" s="4" t="n"/>
+      <c r="L18" s="4" t="n"/>
+      <c r="M18" s="4" t="n"/>
+      <c r="N18" s="4" t="n"/>
+      <c r="O18" s="4" t="n"/>
+      <c r="P18" s="4" t="n"/>
       <c r="Q18" s="4" t="inlineStr">
         <is>
           <t>D0=262.25; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -9903,24 +9117,12 @@
       <c r="J19" s="4" t="n">
         <v>85.42</v>
       </c>
-      <c r="K19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P19" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K19" s="4" t="n"/>
+      <c r="L19" s="4" t="n"/>
+      <c r="M19" s="4" t="n"/>
+      <c r="N19" s="4" t="n"/>
+      <c r="O19" s="4" t="n"/>
+      <c r="P19" s="4" t="n"/>
       <c r="Q19" s="4" t="inlineStr">
         <is>
           <t>D0=85.42; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -9972,24 +9174,6 @@
       <c r="J20" t="n">
         <v>426.01</v>
       </c>
-      <c r="K20" t="n">
-        <v/>
-      </c>
-      <c r="L20" t="n">
-        <v/>
-      </c>
-      <c r="M20" t="n">
-        <v/>
-      </c>
-      <c r="N20" t="n">
-        <v/>
-      </c>
-      <c r="O20" t="n">
-        <v/>
-      </c>
-      <c r="P20" t="n">
-        <v/>
-      </c>
       <c r="Q20" t="inlineStr">
         <is>
           <t>D0=426.01; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -10041,24 +9225,12 @@
       <c r="J21" s="4" t="n">
         <v>13.02</v>
       </c>
-      <c r="K21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P21" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K21" s="4" t="n"/>
+      <c r="L21" s="4" t="n"/>
+      <c r="M21" s="4" t="n"/>
+      <c r="N21" s="4" t="n"/>
+      <c r="O21" s="4" t="n"/>
+      <c r="P21" s="4" t="n"/>
       <c r="Q21" s="4" t="inlineStr">
         <is>
           <t>D0=13.02; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -10295,24 +9467,12 @@
       <c r="J33" s="4" t="n">
         <v>41.47</v>
       </c>
-      <c r="K33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P33" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K33" s="4" t="n"/>
+      <c r="L33" s="4" t="n"/>
+      <c r="M33" s="4" t="n"/>
+      <c r="N33" s="4" t="n"/>
+      <c r="O33" s="4" t="n"/>
+      <c r="P33" s="4" t="n"/>
       <c r="Q33" s="4" t="inlineStr">
         <is>
           <t>D0=41.47; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -10357,11 +9517,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10373,7 +9528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -10551,7 +9706,6 @@
       <c r="E7" t="n">
         <v>107.23</v>
       </c>
-      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -10623,7 +9777,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
@@ -10675,7 +9829,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
@@ -10707,7 +9861,6 @@
       <c r="E13" t="n">
         <v>82.545</v>
       </c>
-      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -10759,7 +9912,6 @@
       <c r="E15" t="n">
         <v>338.585</v>
       </c>
-      <c r="F15" t="inlineStr"/>
     </row>
     <row r="16"/>
     <row r="17">
@@ -11124,8 +10276,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40"/>
-    <row r="41"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
